--- a/artfynd/A 16012-2023 artfynd.xlsx
+++ b/artfynd/A 16012-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 16012-2023 artfynd.xlsx
+++ b/artfynd/A 16012-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>97055941</v>
       </c>
       <c r="B2" t="n">
-        <v>88853</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91330</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +700,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542986.786431934</v>
+        <v>542987</v>
       </c>
       <c r="R2" t="n">
-        <v>6603207.68371876</v>
+        <v>6603207</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,19 +754,9 @@
           <t>2021-11-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-11-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -812,12 +797,7 @@
         <v>102326374</v>
       </c>
       <c r="B3" t="n">
-        <v>108203</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111399</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -865,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543150.9231081165</v>
+        <v>543151</v>
       </c>
       <c r="R3" t="n">
-        <v>6602972.887042124</v>
+        <v>6602973</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,19 +878,9 @@
           <t>2022-07-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-07-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -940,6 +910,125 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>86510875</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99156</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>S Kusktorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>542886</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6603271</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kolsva</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2020-06-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2020-06-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>10 på norra sidan, 10 på södra sidan</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kenneth Nordberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kenneth Nordberg, Tina Nordberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16012-2023 artfynd.xlsx
+++ b/artfynd/A 16012-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97055941</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102326374</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,8 +1044,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86510875</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>